--- a/InputData/trans/RPEF/Retail Price Equivalent Factor.xlsx
+++ b/InputData/trans/RPEF/Retail Price Equivalent Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\RPEF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\RPEF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{39502BE2-C6DB-4BB4-A277-8DB7845D96C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C26EA5F-04CD-4C33-B3FF-D78E947750F2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60FCEBE-E7D7-466E-B619-1756402D7BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,8 @@
     <definedName name="ti_tbl_50">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -48,10 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
-  <si>
-    <t>RPEF Retail Price Equivalent Factor</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>Sources:</t>
   </si>
@@ -59,37 +51,7 @@
     <t>LDVs</t>
   </si>
   <si>
-    <t>EPA</t>
-  </si>
-  <si>
-    <t>Automobile Industry Retail Price Equivalent and Indirect Cost Multipliers</t>
-  </si>
-  <si>
-    <t>https://nepis.epa.gov/Exe/ZyNET.exe/P100AGJ1.TXT?ZyActionD=ZyDocument&amp;Client=EPA&amp;Index=2006+Thru+2010&amp;Docs=&amp;Query=&amp;Time=&amp;EndTime=&amp;SearchMethod=1&amp;TocRestrict=n&amp;Toc=&amp;TocEntry=&amp;QField=&amp;QFieldYear=&amp;QFieldMonth=&amp;QFieldDay=&amp;IntQFieldOp=0&amp;ExtQFieldOp=0&amp;XmlQuery=&amp;File=D%3A%5Czyfiles%5CIndex%20Data%5C06thru10%5CTxt%5C00000025%5CP100AGJ1.txt&amp;User=ANONYMOUS&amp;Password=anonymous&amp;SortMethod=h%7C-&amp;MaximumDocuments=1&amp;FuzzyDegree=0&amp;ImageQuality=r75g8/r75g8/x150y150g16/i425&amp;Display=hpfr&amp;DefSeekPage=x&amp;SearchBack=ZyActionL&amp;Back=ZyActionS&amp;BackDesc=Results%20page&amp;MaximumPages=1&amp;ZyEntry=1&amp;SeekPage=x&amp;ZyPURL</t>
-  </si>
-  <si>
     <t>HDVs</t>
-  </si>
-  <si>
-    <t>Heavy Duty Truck Retail Price Equivalent and Indirect Cost Multipliers</t>
-  </si>
-  <si>
-    <t>https://nepis.epa.gov/Exe/ZyNET.exe/P100XXR3.TXT?ZyActionD=ZyDocument&amp;Client=EPA&amp;Index=2006+Thru+2010&amp;Docs=&amp;Query=&amp;Time=&amp;EndTime=&amp;SearchMethod=1&amp;TocRestrict=n&amp;Toc=&amp;TocEntry=&amp;QField=&amp;QFieldYear=&amp;QFieldMonth=&amp;QFieldDay=&amp;IntQFieldOp=0&amp;ExtQFieldOp=0&amp;XmlQuery=&amp;File=D%3A%5Czyfiles%5CIndex%20Data%5C06thru10%5CTxt%5C00000042%5CP100XXR3.txt&amp;User=ANONYMOUS&amp;Password=anonymous&amp;SortMethod=h%7C-&amp;MaximumDocuments=1&amp;FuzzyDegree=0&amp;ImageQuality=r75g8/r75g8/x150y150g16/i425&amp;Display=hpfr&amp;DefSeekPage=x&amp;SearchBack=ZyActionL&amp;Back=ZyActionS&amp;BackDesc=Results%20page&amp;MaximumPages=1&amp;ZyEntry=1&amp;SeekPage=x&amp;ZyPURL#</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Values should account for the price markup difference between vehicle manufacturing costs and final vehicle retail costs</t>
-  </si>
-  <si>
-    <t>Retail Price Equivalent Factor (Dmnl)</t>
-  </si>
-  <si>
-    <t>Passenger</t>
-  </si>
-  <si>
-    <t>Freight</t>
   </si>
   <si>
     <t>aircraft</t>
@@ -102,6 +64,36 @@
   </si>
   <si>
     <t>motorbikes</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>RPEF Retail Price Equivalent Factor</t>
+  </si>
+  <si>
+    <t>Retail Price Equivalent Factor (Dmnl)</t>
+  </si>
+  <si>
+    <t>Passenger</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>EPA</t>
+  </si>
+  <si>
+    <t>https://nepis.epa.gov/Exe/ZyNET.exe/P100AGJ1.TXT?ZyActionD=ZyDocument&amp;Client=EPA&amp;Index=2006+Thru+2010&amp;Docs=&amp;Query=&amp;Time=&amp;EndTime=&amp;SearchMethod=1&amp;TocRestrict=n&amp;Toc=&amp;TocEntry=&amp;QField=&amp;QFieldYear=&amp;QFieldMonth=&amp;QFieldDay=&amp;IntQFieldOp=0&amp;ExtQFieldOp=0&amp;XmlQuery=&amp;File=D%3A%5Czyfiles%5CIndex%20Data%5C06thru10%5CTxt%5C00000025%5CP100AGJ1.txt&amp;User=ANONYMOUS&amp;Password=anonymous&amp;SortMethod=h%7C-&amp;MaximumDocuments=1&amp;FuzzyDegree=0&amp;ImageQuality=r75g8/r75g8/x150y150g16/i425&amp;Display=hpfr&amp;DefSeekPage=x&amp;SearchBack=ZyActionL&amp;Back=ZyActionS&amp;BackDesc=Results%20page&amp;MaximumPages=1&amp;ZyEntry=1&amp;SeekPage=x&amp;ZyPURL</t>
+  </si>
+  <si>
+    <t>Automobile Industry Retail Price Equivalent and Indirect Cost Multipliers</t>
+  </si>
+  <si>
+    <t>Heavy Duty Truck Retail Price Equivalent and Indirect Cost Multipliers</t>
+  </si>
+  <si>
+    <t>https://nepis.epa.gov/Exe/ZyNET.exe/P100XXR3.TXT?ZyActionD=ZyDocument&amp;Client=EPA&amp;Index=2006+Thru+2010&amp;Docs=&amp;Query=&amp;Time=&amp;EndTime=&amp;SearchMethod=1&amp;TocRestrict=n&amp;Toc=&amp;TocEntry=&amp;QField=&amp;QFieldYear=&amp;QFieldMonth=&amp;QFieldDay=&amp;IntQFieldOp=0&amp;ExtQFieldOp=0&amp;XmlQuery=&amp;File=D%3A%5Czyfiles%5CIndex%20Data%5C06thru10%5CTxt%5C00000042%5CP100XXR3.txt&amp;User=ANONYMOUS&amp;Password=anonymous&amp;SortMethod=h%7C-&amp;MaximumDocuments=1&amp;FuzzyDegree=0&amp;ImageQuality=r75g8/r75g8/x150y150g16/i425&amp;Display=hpfr&amp;DefSeekPage=x&amp;SearchBack=ZyActionL&amp;Back=ZyActionS&amp;BackDesc=Results%20page&amp;MaximumPages=1&amp;ZyEntry=1&amp;SeekPage=x&amp;ZyPURL#</t>
   </si>
 </sst>
 </file>
@@ -1506,28 +1498,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="85.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="85.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1537,22 +1529,22 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1562,20 +1554,17 @@
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30.75">
+    <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1590,21 +1579,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45">
+    <row r="1" spans="1:37" ht="43.5">
       <c r="A1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="1"/>
@@ -1643,13 +1632,13 @@
     </row>
     <row r="2" spans="1:37">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>1.5</v>
       </c>
       <c r="C2" s="4">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1688,7 +1677,7 @@
     </row>
     <row r="3" spans="1:37">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4">
         <v>1.2</v>
@@ -1733,7 +1722,7 @@
     </row>
     <row r="4" spans="1:37">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
@@ -1778,7 +1767,7 @@
     </row>
     <row r="5" spans="1:37">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -1823,7 +1812,7 @@
     </row>
     <row r="6" spans="1:37">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -1868,7 +1857,7 @@
     </row>
     <row r="7" spans="1:37">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
@@ -1915,175 +1904,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1B63-45F5-486B-B984-63B21F44C7B8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780CA153-E2C5-4010-A2A3-A89E6605C10C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20B20272-D6E0-4831-92E3-5C0571EBEEE9}"/>
 </file>